--- a/AAII_Financials/Yearly/VRN_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/VRN_YR_FIN.xlsx
@@ -305,7 +305,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="[$-409]d\-mmm\-yy;@"/>
+    <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yy;@"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -347,7 +347,7 @@
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>

--- a/AAII_Financials/Yearly/VRN_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/VRN_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="92">
   <si>
     <t>VRN</t>
   </si>
@@ -662,8 +662,9 @@
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="9" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="11" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
@@ -709,25 +710,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>3189900</v>
+        <v>2415400</v>
       </c>
       <c r="E8" s="3">
-        <v>3512300</v>
+        <v>2595100</v>
       </c>
       <c r="F8" s="3">
-        <v>2829400</v>
+        <v>2235800</v>
       </c>
       <c r="G8" s="3">
-        <v>1488000</v>
+        <v>1167800</v>
       </c>
       <c r="H8" s="3">
-        <v>2877100</v>
+        <v>2218200</v>
       </c>
       <c r="I8" s="3">
-        <v>3320500</v>
+        <v>2433400</v>
       </c>
       <c r="J8" s="3">
-        <v>2858700</v>
+        <v>2279500</v>
       </c>
       <c r="K8" s="3"/>
     </row>
@@ -736,25 +737,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>839100</v>
+        <v>767400</v>
       </c>
       <c r="E9" s="3">
-        <v>731100</v>
+        <v>637000</v>
       </c>
       <c r="F9" s="3">
-        <v>657900</v>
+        <v>612900</v>
       </c>
       <c r="G9" s="3">
-        <v>574000</v>
+        <v>529800</v>
       </c>
       <c r="H9" s="3">
-        <v>753000</v>
+        <v>675900</v>
       </c>
       <c r="I9" s="3">
-        <v>877800</v>
+        <v>739800</v>
       </c>
       <c r="J9" s="3">
-        <v>835000</v>
+        <v>772500</v>
       </c>
       <c r="K9" s="3"/>
     </row>
@@ -763,25 +764,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>2350800</v>
+        <v>1648100</v>
       </c>
       <c r="E10" s="3">
-        <v>2781200</v>
+        <v>1958200</v>
       </c>
       <c r="F10" s="3">
-        <v>2171500</v>
+        <v>1622900</v>
       </c>
       <c r="G10" s="3">
-        <v>914000</v>
+        <v>638000</v>
       </c>
       <c r="H10" s="3">
-        <v>2124100</v>
+        <v>1542300</v>
       </c>
       <c r="I10" s="3">
-        <v>2442700</v>
+        <v>1693600</v>
       </c>
       <c r="J10" s="3">
-        <v>2023700</v>
+        <v>1507000</v>
       </c>
       <c r="K10" s="3"/>
     </row>
@@ -857,25 +858,25 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>137600</v>
+        <v>30700</v>
       </c>
       <c r="E14" s="3">
-        <v>-401300</v>
+        <v>-15900</v>
       </c>
       <c r="F14" s="3">
-        <v>-2596100</v>
+        <v>-44300</v>
       </c>
       <c r="G14" s="3">
-        <v>3231900</v>
+        <v>-243200</v>
       </c>
       <c r="H14" s="3">
-        <v>1671900</v>
+        <v>140800</v>
       </c>
       <c r="I14" s="3">
-        <v>3840100</v>
+        <v>126600</v>
       </c>
       <c r="J14" s="3">
-        <v>176200</v>
+        <v>-19100</v>
       </c>
       <c r="K14" s="3"/>
     </row>
@@ -884,25 +885,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>894700</v>
+        <v>748500</v>
       </c>
       <c r="E15" s="3">
-        <v>1758900</v>
+        <v>332400</v>
       </c>
       <c r="F15" s="3">
-        <v>786100</v>
+        <v>-1365700</v>
       </c>
       <c r="G15" s="3">
-        <v>712700</v>
+        <v>3351500</v>
       </c>
       <c r="H15" s="3">
-        <v>1246900</v>
+        <v>2091900</v>
       </c>
       <c r="I15" s="3">
-        <v>1578800</v>
+        <v>3872100</v>
       </c>
       <c r="J15" s="3">
-        <v>1537800</v>
+        <v>1388600</v>
       </c>
       <c r="K15" s="3"/>
     </row>
@@ -921,25 +922,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>2181200</v>
+        <v>1493000</v>
       </c>
       <c r="E17" s="3">
-        <v>1394700</v>
+        <v>1392000</v>
       </c>
       <c r="F17" s="3">
-        <v>-899400</v>
+        <v>-293200</v>
       </c>
       <c r="G17" s="3">
-        <v>4719800</v>
+        <v>3793200</v>
       </c>
       <c r="H17" s="3">
-        <v>3897100</v>
+        <v>2910300</v>
       </c>
       <c r="I17" s="3">
-        <v>6622700</v>
+        <v>4779600</v>
       </c>
       <c r="J17" s="3">
-        <v>2869900</v>
+        <v>2224800</v>
       </c>
       <c r="K17" s="3"/>
     </row>
@@ -948,25 +949,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>1008700</v>
+        <v>922400</v>
       </c>
       <c r="E18" s="3">
-        <v>2117600</v>
+        <v>1203200</v>
       </c>
       <c r="F18" s="3">
-        <v>3728800</v>
+        <v>2529100</v>
       </c>
       <c r="G18" s="3">
-        <v>-3231800</v>
+        <v>-2625400</v>
       </c>
       <c r="H18" s="3">
-        <v>-1020000</v>
+        <v>-692100</v>
       </c>
       <c r="I18" s="3">
-        <v>-3302200</v>
+        <v>-2346100</v>
       </c>
       <c r="J18" s="3">
-        <v>-11200</v>
+        <v>54700</v>
       </c>
       <c r="K18" s="3"/>
     </row>
@@ -988,25 +989,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>170400</v>
+        <v>-7600</v>
       </c>
       <c r="E20" s="3">
-        <v>-491100</v>
+        <v>13900</v>
       </c>
       <c r="F20" s="3">
-        <v>-476100</v>
+        <v>-3500</v>
       </c>
       <c r="G20" s="3">
-        <v>178900</v>
+        <v>-3200</v>
       </c>
       <c r="H20" s="3">
-        <v>-25500</v>
+        <v>-51900</v>
       </c>
       <c r="I20" s="3">
-        <v>-68800</v>
+        <v>12900</v>
       </c>
       <c r="J20" s="3">
-        <v>149900</v>
+        <v>-30900</v>
       </c>
       <c r="K20" s="3"/>
     </row>
@@ -1015,25 +1016,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>2244100</v>
+        <v>1678500</v>
       </c>
       <c r="E21" s="3">
-        <v>2578200</v>
+        <v>1521700</v>
       </c>
       <c r="F21" s="3">
-        <v>4038800</v>
+        <v>1166800</v>
       </c>
       <c r="G21" s="3">
-        <v>1217600</v>
+        <v>729300</v>
       </c>
       <c r="H21" s="3">
-        <v>1667800</v>
+        <v>1451700</v>
       </c>
       <c r="I21" s="3">
-        <v>1913700</v>
+        <v>1513000</v>
       </c>
       <c r="J21" s="3">
-        <v>1880100</v>
+        <v>1474100</v>
       </c>
       <c r="K21" s="3"/>
     </row>
@@ -1042,25 +1043,25 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>126000</v>
+        <v>101900</v>
       </c>
       <c r="E22" s="3">
-        <v>64700</v>
+        <v>51200</v>
       </c>
       <c r="F22" s="3">
-        <v>88900</v>
+        <v>76700</v>
       </c>
       <c r="G22" s="3">
-        <v>94600</v>
+        <v>91200</v>
       </c>
       <c r="H22" s="3">
-        <v>146800</v>
+        <v>138200</v>
       </c>
       <c r="I22" s="3">
-        <v>184400</v>
+        <v>120000</v>
       </c>
       <c r="J22" s="3">
-        <v>162300</v>
+        <v>123500</v>
       </c>
       <c r="K22" s="3"/>
     </row>
@@ -1069,25 +1070,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>1053100</v>
+        <v>797400</v>
       </c>
       <c r="E23" s="3">
-        <v>1561800</v>
+        <v>1154000</v>
       </c>
       <c r="F23" s="3">
-        <v>3163800</v>
+        <v>2500100</v>
       </c>
       <c r="G23" s="3">
-        <v>-3147500</v>
+        <v>-2470200</v>
       </c>
       <c r="H23" s="3">
-        <v>-1192300</v>
+        <v>-919300</v>
       </c>
       <c r="I23" s="3">
-        <v>-3555400</v>
+        <v>-2605600</v>
       </c>
       <c r="J23" s="3">
-        <v>-23600</v>
+        <v>-18800</v>
       </c>
       <c r="K23" s="3"/>
     </row>
@@ -1096,25 +1097,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>253700</v>
+        <v>192100</v>
       </c>
       <c r="E24" s="3">
-        <v>415100</v>
+        <v>306700</v>
       </c>
       <c r="F24" s="3">
-        <v>799700</v>
+        <v>631900</v>
       </c>
       <c r="G24" s="3">
-        <v>-627600</v>
+        <v>-492500</v>
       </c>
       <c r="H24" s="3">
-        <v>-159000</v>
+        <v>-122600</v>
       </c>
       <c r="I24" s="3">
-        <v>-938500</v>
+        <v>-687800</v>
       </c>
       <c r="J24" s="3">
-        <v>-7100</v>
+        <v>80100</v>
       </c>
       <c r="K24" s="3"/>
     </row>
@@ -1150,25 +1151,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>799400</v>
+        <v>605300</v>
       </c>
       <c r="E26" s="3">
-        <v>1146700</v>
+        <v>847300</v>
       </c>
       <c r="F26" s="3">
-        <v>2364100</v>
+        <v>1868100</v>
       </c>
       <c r="G26" s="3">
-        <v>-2519900</v>
+        <v>-1977600</v>
       </c>
       <c r="H26" s="3">
-        <v>-1033300</v>
+        <v>-796700</v>
       </c>
       <c r="I26" s="3">
-        <v>-2616900</v>
+        <v>-1917800</v>
       </c>
       <c r="J26" s="3">
-        <v>-16500</v>
+        <v>-98900</v>
       </c>
       <c r="K26" s="3"/>
     </row>
@@ -1177,25 +1178,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>799400</v>
+        <v>431800</v>
       </c>
       <c r="E27" s="3">
-        <v>1146700</v>
+        <v>1096000</v>
       </c>
       <c r="F27" s="3">
-        <v>2364100</v>
+        <v>1868100</v>
       </c>
       <c r="G27" s="3">
-        <v>-2519900</v>
+        <v>-1977600</v>
       </c>
       <c r="H27" s="3">
-        <v>-1033300</v>
+        <v>-796700</v>
       </c>
       <c r="I27" s="3">
-        <v>-2616900</v>
+        <v>-1917800</v>
       </c>
       <c r="J27" s="3">
-        <v>-16500</v>
+        <v>-98900</v>
       </c>
       <c r="K27" s="3"/>
     </row>
@@ -1231,25 +1232,25 @@
         <v>24</v>
       </c>
       <c r="D29" s="3">
-        <v>-229100</v>
+        <v>-173500</v>
       </c>
       <c r="E29" s="3">
-        <v>336700</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I29" s="3" t="s">
-        <v>8</v>
+        <v>248800</v>
+      </c>
+      <c r="F29" s="3">
+        <v>0</v>
+      </c>
+      <c r="G29" s="3">
+        <v>0</v>
+      </c>
+      <c r="H29" s="3">
+        <v>0</v>
+      </c>
+      <c r="I29" s="3">
+        <v>0</v>
       </c>
       <c r="J29" s="3">
-        <v>-107500</v>
+        <v>0</v>
       </c>
       <c r="K29" s="3"/>
     </row>
@@ -1312,25 +1313,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-170400</v>
+        <v>7600</v>
       </c>
       <c r="E32" s="3">
-        <v>491100</v>
+        <v>-13900</v>
       </c>
       <c r="F32" s="3">
-        <v>476100</v>
+        <v>3500</v>
       </c>
       <c r="G32" s="3">
-        <v>-178900</v>
+        <v>3200</v>
       </c>
       <c r="H32" s="3">
-        <v>25500</v>
+        <v>51900</v>
       </c>
       <c r="I32" s="3">
-        <v>68800</v>
+        <v>-12900</v>
       </c>
       <c r="J32" s="3">
-        <v>-149900</v>
+        <v>30900</v>
       </c>
       <c r="K32" s="3"/>
     </row>
@@ -1339,25 +1340,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>570300</v>
+        <v>431800</v>
       </c>
       <c r="E33" s="3">
-        <v>1483400</v>
+        <v>1096000</v>
       </c>
       <c r="F33" s="3">
-        <v>2364100</v>
+        <v>1868100</v>
       </c>
       <c r="G33" s="3">
-        <v>-2519900</v>
+        <v>-1977600</v>
       </c>
       <c r="H33" s="3">
-        <v>-1033300</v>
+        <v>-796700</v>
       </c>
       <c r="I33" s="3">
-        <v>-2616900</v>
+        <v>-1917800</v>
       </c>
       <c r="J33" s="3">
-        <v>-124000</v>
+        <v>-98900</v>
       </c>
       <c r="K33" s="3"/>
     </row>
@@ -1393,25 +1394,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>570300</v>
+        <v>431800</v>
       </c>
       <c r="E35" s="3">
-        <v>1483400</v>
+        <v>1096000</v>
       </c>
       <c r="F35" s="3">
-        <v>2364100</v>
+        <v>1868100</v>
       </c>
       <c r="G35" s="3">
-        <v>-2519900</v>
+        <v>-1977600</v>
       </c>
       <c r="H35" s="3">
-        <v>-1033300</v>
+        <v>-796700</v>
       </c>
       <c r="I35" s="3">
-        <v>-2616900</v>
+        <v>-1917800</v>
       </c>
       <c r="J35" s="3">
-        <v>-124000</v>
+        <v>-98900</v>
       </c>
       <c r="K35" s="3"/>
     </row>
@@ -1478,25 +1479,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>17300</v>
+        <v>13100</v>
       </c>
       <c r="E41" s="3">
-        <v>289900</v>
+        <v>214200</v>
       </c>
       <c r="F41" s="3">
-        <v>13500</v>
+        <v>10700</v>
       </c>
       <c r="G41" s="3">
-        <v>8800</v>
+        <v>6900</v>
       </c>
       <c r="H41" s="3">
-        <v>56900</v>
+        <v>43900</v>
       </c>
       <c r="I41" s="3">
-        <v>15300</v>
+        <v>11200</v>
       </c>
       <c r="J41" s="3">
-        <v>62400</v>
+        <v>49800</v>
       </c>
       <c r="K41" s="3"/>
     </row>
@@ -1532,25 +1533,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>377900</v>
+        <v>286200</v>
       </c>
       <c r="E43" s="3">
-        <v>327800</v>
+        <v>242200</v>
       </c>
       <c r="F43" s="3">
-        <v>314300</v>
+        <v>248400</v>
       </c>
       <c r="G43" s="3">
-        <v>200500</v>
+        <v>157400</v>
       </c>
       <c r="H43" s="3">
-        <v>295900</v>
+        <v>228100</v>
       </c>
       <c r="I43" s="3">
-        <v>322600</v>
+        <v>236400</v>
       </c>
       <c r="J43" s="3">
-        <v>380200</v>
+        <v>303200</v>
       </c>
       <c r="K43" s="3"/>
     </row>
@@ -1558,26 +1559,26 @@
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K44" s="3"/>
     </row>
@@ -1586,25 +1587,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>654800</v>
+        <v>429300</v>
       </c>
       <c r="E45" s="3">
-        <v>371500</v>
+        <v>226100</v>
       </c>
       <c r="F45" s="3">
-        <v>83100</v>
+        <v>59800</v>
       </c>
       <c r="G45" s="3">
-        <v>69400</v>
+        <v>36700</v>
       </c>
       <c r="H45" s="3">
-        <v>278700</v>
+        <v>209600</v>
       </c>
       <c r="I45" s="3">
-        <v>248700</v>
+        <v>178900</v>
       </c>
       <c r="J45" s="3">
-        <v>66700</v>
+        <v>49600</v>
       </c>
       <c r="K45" s="3"/>
     </row>
@@ -1613,25 +1614,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>1050000</v>
+        <v>795100</v>
       </c>
       <c r="E46" s="3">
-        <v>989200</v>
+        <v>730900</v>
       </c>
       <c r="F46" s="3">
-        <v>410900</v>
+        <v>324700</v>
       </c>
       <c r="G46" s="3">
-        <v>278700</v>
+        <v>218700</v>
       </c>
       <c r="H46" s="3">
-        <v>631500</v>
+        <v>486900</v>
       </c>
       <c r="I46" s="3">
-        <v>586600</v>
+        <v>429900</v>
       </c>
       <c r="J46" s="3">
-        <v>509300</v>
+        <v>406100</v>
       </c>
       <c r="K46" s="3"/>
     </row>
@@ -1639,26 +1640,26 @@
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3" t="s">
-        <v>8</v>
+      <c r="D47" s="3">
+        <v>200</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F47" s="3">
+      <c r="F47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G47" s="3">
+        <v>2000</v>
+      </c>
+      <c r="H47" s="3">
+        <v>5200</v>
+      </c>
+      <c r="I47" s="3">
         <v>6400</v>
       </c>
-      <c r="G47" s="3">
-        <v>18200</v>
-      </c>
-      <c r="H47" s="3">
-        <v>22400</v>
-      </c>
-      <c r="I47" s="3">
-        <v>24500</v>
-      </c>
       <c r="J47" s="3">
-        <v>88400</v>
+        <v>57900</v>
       </c>
       <c r="K47" s="3"/>
     </row>
@@ -1667,25 +1668,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>11428100</v>
+        <v>8653500</v>
       </c>
       <c r="E48" s="3">
-        <v>7911700</v>
+        <v>5845700</v>
       </c>
       <c r="F48" s="3">
-        <v>7827500</v>
+        <v>6185400</v>
       </c>
       <c r="G48" s="3">
-        <v>4562100</v>
+        <v>3580400</v>
       </c>
       <c r="H48" s="3">
-        <v>8210600</v>
+        <v>6330300</v>
       </c>
       <c r="I48" s="3">
-        <v>10902800</v>
+        <v>7990100</v>
       </c>
       <c r="J48" s="3">
-        <v>14697300</v>
+        <v>11719600</v>
       </c>
       <c r="K48" s="3"/>
     </row>
@@ -1694,25 +1695,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>275900</v>
+        <v>208900</v>
       </c>
       <c r="E49" s="3">
-        <v>203900</v>
+        <v>150700</v>
       </c>
       <c r="F49" s="3">
-        <v>211500</v>
+        <v>167100</v>
       </c>
       <c r="G49" s="3">
-        <v>223300</v>
+        <v>175200</v>
       </c>
       <c r="H49" s="3">
-        <v>230900</v>
+        <v>178000</v>
       </c>
       <c r="I49" s="3">
-        <v>244000</v>
+        <v>178800</v>
       </c>
       <c r="J49" s="3">
-        <v>251900</v>
+        <v>200900</v>
       </c>
       <c r="K49" s="3"/>
     </row>
@@ -1775,25 +1776,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>21700</v>
+        <v>16300</v>
       </c>
       <c r="E52" s="3">
-        <v>381600</v>
+        <v>76000</v>
       </c>
       <c r="F52" s="3">
-        <v>714900</v>
+        <v>119500</v>
       </c>
       <c r="G52" s="3">
-        <v>1563600</v>
+        <v>165900</v>
       </c>
       <c r="H52" s="3">
-        <v>996400</v>
+        <v>205700</v>
       </c>
       <c r="I52" s="3">
-        <v>972500</v>
+        <v>282900</v>
       </c>
       <c r="J52" s="3">
-        <v>458400</v>
+        <v>224400</v>
       </c>
       <c r="K52" s="3"/>
     </row>
@@ -1829,25 +1830,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>12775700</v>
+        <v>9673900</v>
       </c>
       <c r="E54" s="3">
-        <v>9486400</v>
+        <v>7009200</v>
       </c>
       <c r="F54" s="3">
-        <v>9171200</v>
+        <v>7247200</v>
       </c>
       <c r="G54" s="3">
-        <v>6645900</v>
+        <v>5215700</v>
       </c>
       <c r="H54" s="3">
-        <v>10091800</v>
+        <v>7780700</v>
       </c>
       <c r="I54" s="3">
-        <v>12730400</v>
+        <v>9329400</v>
       </c>
       <c r="J54" s="3">
-        <v>16005300</v>
+        <v>12762600</v>
       </c>
       <c r="K54" s="3"/>
     </row>
@@ -1882,25 +1883,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>634900</v>
+        <v>480800</v>
       </c>
       <c r="E57" s="3">
-        <v>448200</v>
+        <v>331200</v>
       </c>
       <c r="F57" s="3">
-        <v>450700</v>
+        <v>356100</v>
       </c>
       <c r="G57" s="3">
-        <v>311600</v>
+        <v>243500</v>
       </c>
       <c r="H57" s="3">
-        <v>479400</v>
+        <v>369600</v>
       </c>
       <c r="I57" s="3">
-        <v>532900</v>
+        <v>402600</v>
       </c>
       <c r="J57" s="3">
-        <v>613300</v>
+        <v>489000</v>
       </c>
       <c r="K57" s="3"/>
     </row>
@@ -1909,25 +1910,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>420500</v>
+        <v>318400</v>
       </c>
       <c r="E58" s="3">
-        <v>563600</v>
+        <v>416400</v>
       </c>
       <c r="F58" s="3">
-        <v>303600</v>
+        <v>239900</v>
       </c>
       <c r="G58" s="3">
-        <v>248000</v>
+        <v>194600</v>
       </c>
       <c r="H58" s="3">
-        <v>232300</v>
+        <v>179100</v>
       </c>
       <c r="I58" s="3">
-        <v>99800</v>
+        <v>73100</v>
       </c>
       <c r="J58" s="3">
-        <v>63800</v>
+        <v>50900</v>
       </c>
       <c r="K58" s="3"/>
     </row>
@@ -1936,25 +1937,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>318100</v>
+        <v>212500</v>
       </c>
       <c r="E59" s="3">
-        <v>227200</v>
+        <v>131600</v>
       </c>
       <c r="F59" s="3">
-        <v>277900</v>
+        <v>187500</v>
       </c>
       <c r="G59" s="3">
-        <v>109600</v>
+        <v>79200</v>
       </c>
       <c r="H59" s="3">
-        <v>63600</v>
+        <v>47300</v>
       </c>
       <c r="I59" s="3">
-        <v>55900</v>
+        <v>24100</v>
       </c>
       <c r="J59" s="3">
-        <v>186400</v>
+        <v>134500</v>
       </c>
       <c r="K59" s="3"/>
     </row>
@@ -1963,25 +1964,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>1373500</v>
+        <v>1040000</v>
       </c>
       <c r="E60" s="3">
-        <v>1239000</v>
+        <v>915500</v>
       </c>
       <c r="F60" s="3">
-        <v>1032200</v>
+        <v>815700</v>
       </c>
       <c r="G60" s="3">
-        <v>669200</v>
+        <v>525200</v>
       </c>
       <c r="H60" s="3">
-        <v>775300</v>
+        <v>597700</v>
       </c>
       <c r="I60" s="3">
+        <v>504600</v>
+      </c>
+      <c r="J60" s="3">
         <v>688600</v>
-      </c>
-      <c r="J60" s="3">
-        <v>863500</v>
       </c>
       <c r="K60" s="3"/>
     </row>
@@ -1990,25 +1991,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>3290500</v>
+        <v>2491600</v>
       </c>
       <c r="E61" s="3">
-        <v>1002000</v>
+        <v>740300</v>
       </c>
       <c r="F61" s="3">
-        <v>1808000</v>
+        <v>1428700</v>
       </c>
       <c r="G61" s="3">
-        <v>2168100</v>
+        <v>1701500</v>
       </c>
       <c r="H61" s="3">
-        <v>2854000</v>
+        <v>2200400</v>
       </c>
       <c r="I61" s="3">
-        <v>4176900</v>
+        <v>3061000</v>
       </c>
       <c r="J61" s="3">
-        <v>4047200</v>
+        <v>3227200</v>
       </c>
       <c r="K61" s="3"/>
     </row>
@@ -2017,25 +2018,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>1244200</v>
+        <v>455200</v>
       </c>
       <c r="E62" s="3">
-        <v>752000</v>
+        <v>498500</v>
       </c>
       <c r="F62" s="3">
-        <v>925700</v>
+        <v>731500</v>
       </c>
       <c r="G62" s="3">
-        <v>985800</v>
+        <v>773700</v>
       </c>
       <c r="H62" s="3">
-        <v>1119800</v>
+        <v>863400</v>
       </c>
       <c r="I62" s="3">
-        <v>1252100</v>
+        <v>917600</v>
       </c>
       <c r="J62" s="3">
-        <v>1931700</v>
+        <v>1101300</v>
       </c>
       <c r="K62" s="3"/>
     </row>
@@ -2125,25 +2126,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>5908200</v>
+        <v>4473800</v>
       </c>
       <c r="E66" s="3">
-        <v>2993000</v>
+        <v>2211400</v>
       </c>
       <c r="F66" s="3">
-        <v>3765900</v>
+        <v>2975800</v>
       </c>
       <c r="G66" s="3">
-        <v>3823100</v>
+        <v>3000400</v>
       </c>
       <c r="H66" s="3">
-        <v>4749100</v>
+        <v>3661500</v>
       </c>
       <c r="I66" s="3">
-        <v>6117600</v>
+        <v>4483300</v>
       </c>
       <c r="J66" s="3">
-        <v>6842400</v>
+        <v>5456100</v>
       </c>
       <c r="K66" s="3"/>
     </row>
@@ -2273,25 +2274,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-10202500</v>
+        <v>-7725500</v>
       </c>
       <c r="E72" s="3">
-        <v>-10563300</v>
+        <v>-7804900</v>
       </c>
       <c r="F72" s="3">
-        <v>-11848700</v>
+        <v>-9362900</v>
       </c>
       <c r="G72" s="3">
-        <v>-14166100</v>
+        <v>-11117600</v>
       </c>
       <c r="H72" s="3">
-        <v>-11636900</v>
+        <v>-8971900</v>
       </c>
       <c r="I72" s="3">
-        <v>-10567200</v>
+        <v>-7744100</v>
       </c>
       <c r="J72" s="3">
-        <v>-7751800</v>
+        <v>-6181300</v>
       </c>
       <c r="K72" s="3"/>
     </row>
@@ -2381,25 +2382,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>6867500</v>
+        <v>5200200</v>
       </c>
       <c r="E76" s="3">
-        <v>6493400</v>
+        <v>4797800</v>
       </c>
       <c r="F76" s="3">
-        <v>5405300</v>
+        <v>4271300</v>
       </c>
       <c r="G76" s="3">
-        <v>2822800</v>
+        <v>2215400</v>
       </c>
       <c r="H76" s="3">
-        <v>5342700</v>
+        <v>4119200</v>
       </c>
       <c r="I76" s="3">
-        <v>6612800</v>
+        <v>4846200</v>
       </c>
       <c r="J76" s="3">
-        <v>9162900</v>
+        <v>7306500</v>
       </c>
       <c r="K76" s="3"/>
     </row>
@@ -2467,25 +2468,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>570300</v>
+        <v>431800</v>
       </c>
       <c r="E81" s="3">
-        <v>1483400</v>
+        <v>1096000</v>
       </c>
       <c r="F81" s="3">
-        <v>2364100</v>
+        <v>1868100</v>
       </c>
       <c r="G81" s="3">
-        <v>-2519900</v>
+        <v>-1977600</v>
       </c>
       <c r="H81" s="3">
-        <v>-1033300</v>
+        <v>-796700</v>
       </c>
       <c r="I81" s="3">
-        <v>-2616900</v>
+        <v>-1917800</v>
       </c>
       <c r="J81" s="3">
-        <v>-124000</v>
+        <v>-98900</v>
       </c>
       <c r="K81" s="3"/>
     </row>
@@ -2507,25 +2508,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>1065000</v>
+        <v>677500</v>
       </c>
       <c r="E83" s="3">
-        <v>951700</v>
+        <v>596400</v>
       </c>
       <c r="F83" s="3">
-        <v>786100</v>
+        <v>621200</v>
       </c>
       <c r="G83" s="3">
-        <v>4270500</v>
+        <v>559300</v>
       </c>
       <c r="H83" s="3">
-        <v>2713300</v>
+        <v>961300</v>
       </c>
       <c r="I83" s="3">
-        <v>5284700</v>
+        <v>1157000</v>
       </c>
       <c r="J83" s="3">
-        <v>1741400</v>
+        <v>1226200</v>
       </c>
       <c r="K83" s="3"/>
     </row>
@@ -2669,25 +2670,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>2195700</v>
+        <v>1662600</v>
       </c>
       <c r="E89" s="3">
-        <v>2192200</v>
+        <v>1619700</v>
       </c>
       <c r="F89" s="3">
-        <v>1495800</v>
+        <v>1182000</v>
       </c>
       <c r="G89" s="3">
-        <v>860500</v>
+        <v>675300</v>
       </c>
       <c r="H89" s="3">
-        <v>1742900</v>
+        <v>1343800</v>
       </c>
       <c r="I89" s="3">
-        <v>1748000</v>
+        <v>1281000</v>
       </c>
       <c r="J89" s="3">
-        <v>1718700</v>
+        <v>1370500</v>
       </c>
       <c r="K89" s="3"/>
     </row>
@@ -2709,25 +2710,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-4836700</v>
+        <v>-924200</v>
       </c>
       <c r="E91" s="3">
-        <v>-1118100</v>
+        <v>-759100</v>
       </c>
       <c r="F91" s="3">
-        <v>-1354000</v>
+        <v>-534300</v>
       </c>
       <c r="G91" s="3">
-        <v>-700200</v>
+        <v>-548400</v>
       </c>
       <c r="H91" s="3">
-        <v>-1322100</v>
+        <v>-1014500</v>
       </c>
       <c r="I91" s="3">
-        <v>-1833200</v>
+        <v>-1339700</v>
       </c>
       <c r="J91" s="3">
-        <v>-2162800</v>
+        <v>-1721700</v>
       </c>
       <c r="K91" s="3"/>
     </row>
@@ -2790,25 +2791,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-4237200</v>
+        <v>-3208500</v>
       </c>
       <c r="E94" s="3">
-        <v>-860600</v>
+        <v>-635900</v>
       </c>
       <c r="F94" s="3">
-        <v>-1193400</v>
+        <v>-943000</v>
       </c>
       <c r="G94" s="3">
-        <v>-269000</v>
+        <v>-211100</v>
       </c>
       <c r="H94" s="3">
-        <v>-345000</v>
+        <v>-266000</v>
       </c>
       <c r="I94" s="3">
-        <v>-1509400</v>
+        <v>-1106200</v>
       </c>
       <c r="J94" s="3">
-        <v>-1960200</v>
+        <v>-1563100</v>
       </c>
       <c r="K94" s="3"/>
     </row>
@@ -2830,25 +2831,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-211900</v>
+        <v>124300</v>
       </c>
       <c r="E96" s="3">
-        <v>-200600</v>
+        <v>133900</v>
       </c>
       <c r="F96" s="3">
-        <v>-47800</v>
+        <v>37800</v>
       </c>
       <c r="G96" s="3">
-        <v>-9400</v>
+        <v>7400</v>
       </c>
       <c r="H96" s="3">
-        <v>-22000</v>
+        <v>17000</v>
       </c>
       <c r="I96" s="3">
-        <v>-198500</v>
+        <v>145500</v>
       </c>
       <c r="J96" s="3">
-        <v>-197700</v>
+        <v>157600</v>
       </c>
       <c r="K96" s="3"/>
     </row>
@@ -2938,25 +2939,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>1768900</v>
+        <v>1339400</v>
       </c>
       <c r="E100" s="3">
-        <v>-1056000</v>
+        <v>-780200</v>
       </c>
       <c r="F100" s="3">
-        <v>-297200</v>
+        <v>-234800</v>
       </c>
       <c r="G100" s="3">
-        <v>-639500</v>
+        <v>-501900</v>
       </c>
       <c r="H100" s="3">
-        <v>-1355700</v>
+        <v>-1045200</v>
       </c>
       <c r="I100" s="3">
-        <v>-287900</v>
+        <v>-211000</v>
       </c>
       <c r="J100" s="3">
-        <v>291200</v>
+        <v>232200</v>
       </c>
       <c r="K100" s="3"/>
     </row>
@@ -2964,26 +2965,26 @@
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E101" s="3">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="F101" s="3">
-        <v>-500</v>
+        <v>-400</v>
       </c>
       <c r="G101" s="3">
         <v>-100</v>
       </c>
       <c r="H101" s="3">
+        <v>-500</v>
+      </c>
+      <c r="I101" s="3">
+        <v>1600</v>
+      </c>
+      <c r="J101" s="3">
         <v>-600</v>
-      </c>
-      <c r="I101" s="3">
-        <v>2200</v>
-      </c>
-      <c r="J101" s="3">
-        <v>-700</v>
       </c>
       <c r="K101" s="3"/>
     </row>
@@ -2992,25 +2993,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-272600</v>
+        <v>-206400</v>
       </c>
       <c r="E102" s="3">
-        <v>276400</v>
+        <v>204200</v>
       </c>
       <c r="F102" s="3">
-        <v>4700</v>
+        <v>3700</v>
       </c>
       <c r="G102" s="3">
-        <v>-48100</v>
+        <v>-37700</v>
       </c>
       <c r="H102" s="3">
-        <v>41600</v>
+        <v>32100</v>
       </c>
       <c r="I102" s="3">
-        <v>-47100</v>
+        <v>-34500</v>
       </c>
       <c r="J102" s="3">
-        <v>49000</v>
+        <v>39100</v>
       </c>
       <c r="K102" s="3"/>
     </row>

--- a/AAII_Financials/Yearly/VRN_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/VRN_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="92">
   <si>
     <t>VRN</t>
   </si>
@@ -656,137 +656,149 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:K102"/>
+  <dimension ref="A5:L102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44561</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44196</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43830</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43465</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43100</v>
       </c>
-      <c r="K7" s="2"/>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L7" s="2"/>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>2760700</v>
+      </c>
+      <c r="E8" s="3">
         <v>2415400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>2595100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>2235800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1167800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>2218200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>2433400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>2279500</v>
       </c>
-      <c r="K8" s="3"/>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L8" s="3"/>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>970000</v>
+      </c>
+      <c r="E9" s="3">
         <v>767400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>637000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>612900</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>529800</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>675900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>739800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>772500</v>
       </c>
-      <c r="K9" s="3"/>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L9" s="3"/>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1790700</v>
+      </c>
+      <c r="E10" s="3">
         <v>1648100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1958200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1622900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>638000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1542300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1693600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1507000</v>
       </c>
-      <c r="K10" s="3"/>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L10" s="3"/>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -798,8 +810,9 @@
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L11" s="3"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -824,9 +837,12 @@
       <c r="J12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K12" s="3"/>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L12" s="3"/>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -851,63 +867,72 @@
       <c r="J13" s="3">
         <v>0</v>
       </c>
-      <c r="K13" s="3"/>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K13" s="3">
+        <v>0</v>
+      </c>
+      <c r="L13" s="3"/>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>38600</v>
+      </c>
+      <c r="E14" s="3">
         <v>30700</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-15900</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-44300</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-243200</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>140800</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>126600</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-19100</v>
       </c>
-      <c r="K14" s="3"/>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L14" s="3"/>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>1268500</v>
+      </c>
+      <c r="E15" s="3">
         <v>748500</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>332400</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>-1365700</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>3351500</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>2091900</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>3872100</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>1388600</v>
       </c>
-      <c r="K15" s="3"/>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L15" s="3"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -916,62 +941,69 @@
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
-    </row>
-    <row r="17" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L16" s="3"/>
+    </row>
+    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2342600</v>
+      </c>
+      <c r="E17" s="3">
         <v>1493000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1392000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>-293200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>3793200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>2910300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>4779600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>2224800</v>
       </c>
-      <c r="K17" s="3"/>
-    </row>
-    <row r="18" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L17" s="3"/>
+    </row>
+    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>418100</v>
+      </c>
+      <c r="E18" s="3">
         <v>922400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>1203200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>2529100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-2625400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-692100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-2346100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>54700</v>
       </c>
-      <c r="K18" s="3"/>
-    </row>
-    <row r="19" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L18" s="3"/>
+    </row>
+    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -983,143 +1015,159 @@
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
-    </row>
-    <row r="20" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L19" s="3"/>
+    </row>
+    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="E20" s="3">
         <v>-7600</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>13900</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-3500</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-3200</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-51900</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>12900</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-30900</v>
       </c>
-      <c r="K20" s="3"/>
-    </row>
-    <row r="21" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L20" s="3"/>
+    </row>
+    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>1690700</v>
+      </c>
+      <c r="E21" s="3">
         <v>1678500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>1521700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1166800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>729300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>1451700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1513000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1474100</v>
       </c>
-      <c r="K21" s="3"/>
-    </row>
-    <row r="22" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L21" s="3"/>
+    </row>
+    <row r="22" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>144800</v>
+      </c>
+      <c r="E22" s="3">
         <v>101900</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>51200</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>76700</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>91200</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>138200</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>120000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>123500</v>
       </c>
-      <c r="K22" s="3"/>
-    </row>
-    <row r="23" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L22" s="3"/>
+    </row>
+    <row r="23" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>238900</v>
+      </c>
+      <c r="E23" s="3">
         <v>797400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1154000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>2500100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-2470200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-919300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-2605600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-18800</v>
       </c>
-      <c r="K23" s="3"/>
-    </row>
-    <row r="24" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L23" s="3"/>
+    </row>
+    <row r="24" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>41600</v>
+      </c>
+      <c r="E24" s="3">
         <v>192100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>306700</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>631900</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-492500</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-122600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-687800</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>80100</v>
       </c>
-      <c r="K24" s="3"/>
-    </row>
-    <row r="25" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L24" s="3"/>
+    </row>
+    <row r="25" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1144,63 +1192,72 @@
       <c r="J25" s="3">
         <v>0</v>
       </c>
-      <c r="K25" s="3"/>
-    </row>
-    <row r="26" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K25" s="3">
+        <v>0</v>
+      </c>
+      <c r="L25" s="3"/>
+    </row>
+    <row r="26" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>197300</v>
+      </c>
+      <c r="E26" s="3">
         <v>605300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>847300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1868100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-1977600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-796700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-1917800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-98900</v>
       </c>
-      <c r="K26" s="3"/>
-    </row>
-    <row r="27" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L26" s="3"/>
+    </row>
+    <row r="27" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>189900</v>
+      </c>
+      <c r="E27" s="3">
         <v>431800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1096000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1868100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-1977600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-796700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-1917800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-98900</v>
       </c>
-      <c r="K27" s="3"/>
-    </row>
-    <row r="28" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L27" s="3"/>
+    </row>
+    <row r="28" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1225,21 +1282,24 @@
       <c r="J28" s="3">
         <v>0</v>
       </c>
-      <c r="K28" s="3"/>
-    </row>
-    <row r="29" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K28" s="3">
+        <v>0</v>
+      </c>
+      <c r="L28" s="3"/>
+    </row>
+    <row r="29" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="E29" s="3">
         <v>-173500</v>
       </c>
-      <c r="E29" s="3">
+      <c r="F29" s="3">
         <v>248800</v>
       </c>
-      <c r="F29" s="3">
-        <v>0</v>
-      </c>
       <c r="G29" s="3">
         <v>0</v>
       </c>
@@ -1252,9 +1312,12 @@
       <c r="J29" s="3">
         <v>0</v>
       </c>
-      <c r="K29" s="3"/>
-    </row>
-    <row r="30" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K29" s="3">
+        <v>0</v>
+      </c>
+      <c r="L29" s="3"/>
+    </row>
+    <row r="30" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1279,9 +1342,12 @@
       <c r="J30" s="3">
         <v>0</v>
       </c>
-      <c r="K30" s="3"/>
-    </row>
-    <row r="31" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K30" s="3">
+        <v>0</v>
+      </c>
+      <c r="L30" s="3"/>
+    </row>
+    <row r="31" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1306,63 +1372,72 @@
       <c r="J31" s="3">
         <v>0</v>
       </c>
-      <c r="K31" s="3"/>
-    </row>
-    <row r="32" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K31" s="3">
+        <v>0</v>
+      </c>
+      <c r="L31" s="3"/>
+    </row>
+    <row r="32" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E32" s="3">
         <v>7600</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-13900</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>3500</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>3200</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>51900</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-12900</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>30900</v>
       </c>
-      <c r="K32" s="3"/>
-    </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L32" s="3"/>
+    </row>
+    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>189900</v>
+      </c>
+      <c r="E33" s="3">
         <v>431800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1096000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1868100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-1977600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-796700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-1917800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-98900</v>
       </c>
-      <c r="K33" s="3"/>
-    </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L33" s="3"/>
+    </row>
+    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1387,68 +1462,77 @@
       <c r="J34" s="3">
         <v>0</v>
       </c>
-      <c r="K34" s="3"/>
-    </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K34" s="3">
+        <v>0</v>
+      </c>
+      <c r="L34" s="3"/>
+    </row>
+    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>189900</v>
+      </c>
+      <c r="E35" s="3">
         <v>431800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1096000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1868100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-1977600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-796700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-1917800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-98900</v>
       </c>
-      <c r="K35" s="3"/>
-    </row>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L35" s="3"/>
+    </row>
+    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44561</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44196</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43830</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43465</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43100</v>
       </c>
-      <c r="K38" s="2"/>
-    </row>
-    <row r="39" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L38" s="2"/>
+    </row>
+    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1460,8 +1544,9 @@
       <c r="I39" s="3"/>
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
-    </row>
-    <row r="40" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L39" s="3"/>
+    </row>
+    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1473,35 +1558,39 @@
       <c r="I40" s="3"/>
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
-    </row>
-    <row r="41" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L40" s="3"/>
+    </row>
+    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>11900</v>
+      </c>
+      <c r="E41" s="3">
         <v>13100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>214200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>10700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>6900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>43900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>11200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>49800</v>
       </c>
-      <c r="K41" s="3"/>
-    </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L41" s="3"/>
+    </row>
+    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1526,36 +1615,42 @@
       <c r="J42" s="3">
         <v>0</v>
       </c>
-      <c r="K42" s="3"/>
-    </row>
-    <row r="43" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3"/>
+    </row>
+    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>268600</v>
+      </c>
+      <c r="E43" s="3">
         <v>286200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>242200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>248400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>157400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>228100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>236400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>303200</v>
       </c>
-      <c r="K43" s="3"/>
-    </row>
-    <row r="44" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L43" s="3"/>
+    </row>
+    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1580,144 +1675,162 @@
       <c r="J44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K44" s="3"/>
-    </row>
-    <row r="45" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L44" s="3"/>
+    </row>
+    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>121000</v>
+      </c>
+      <c r="E45" s="3">
         <v>429300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>226100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>59800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>36700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>209600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>178900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>49600</v>
       </c>
-      <c r="K45" s="3"/>
-    </row>
-    <row r="46" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L45" s="3"/>
+    </row>
+    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>470400</v>
+      </c>
+      <c r="E46" s="3">
         <v>795100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>730900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>324700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>218700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>486900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>429900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>406100</v>
       </c>
-      <c r="K46" s="3"/>
-    </row>
-    <row r="47" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L46" s="3"/>
+    </row>
+    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>100</v>
+      </c>
+      <c r="E47" s="3">
         <v>200</v>
-      </c>
-      <c r="E47" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="F47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G47" s="3">
+      <c r="G47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H47" s="3">
         <v>2000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>5200</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>6400</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>57900</v>
       </c>
-      <c r="K47" s="3"/>
-    </row>
-    <row r="48" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L47" s="3"/>
+    </row>
+    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>7502200</v>
+      </c>
+      <c r="E48" s="3">
         <v>8653500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>5845700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>6185400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>3580400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>6330300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>7990100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>11719600</v>
       </c>
-      <c r="K48" s="3"/>
-    </row>
-    <row r="49" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L48" s="3"/>
+    </row>
+    <row r="49" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>169400</v>
+      </c>
+      <c r="E49" s="3">
         <v>208900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>150700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>167100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>175200</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>178000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>178800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>200900</v>
       </c>
-      <c r="K49" s="3"/>
-    </row>
-    <row r="50" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L49" s="3"/>
+    </row>
+    <row r="50" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1742,9 +1855,12 @@
       <c r="J50" s="3">
         <v>0</v>
       </c>
-      <c r="K50" s="3"/>
-    </row>
-    <row r="51" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K50" s="3">
+        <v>0</v>
+      </c>
+      <c r="L50" s="3"/>
+    </row>
+    <row r="51" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1769,36 +1885,42 @@
       <c r="J51" s="3">
         <v>0</v>
       </c>
-      <c r="K51" s="3"/>
-    </row>
-    <row r="52" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K51" s="3">
+        <v>0</v>
+      </c>
+      <c r="L51" s="3"/>
+    </row>
+    <row r="52" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>24900</v>
+      </c>
+      <c r="E52" s="3">
         <v>16300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>76000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>119500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>165900</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>205700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>282900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>224400</v>
       </c>
-      <c r="K52" s="3"/>
-    </row>
-    <row r="53" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L52" s="3"/>
+    </row>
+    <row r="53" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -1823,36 +1945,42 @@
       <c r="J53" s="3">
         <v>0</v>
       </c>
-      <c r="K53" s="3"/>
-    </row>
-    <row r="54" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K53" s="3">
+        <v>0</v>
+      </c>
+      <c r="L53" s="3"/>
+    </row>
+    <row r="54" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>8167000</v>
+      </c>
+      <c r="E54" s="3">
         <v>9673900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>7009200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>7247200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>5215700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>7780700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>9329400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>12762600</v>
       </c>
-      <c r="K54" s="3"/>
-    </row>
-    <row r="55" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L54" s="3"/>
+    </row>
+    <row r="55" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -1864,8 +1992,9 @@
       <c r="I55" s="3"/>
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
-    </row>
-    <row r="56" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L55" s="3"/>
+    </row>
+    <row r="56" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -1877,170 +2006,189 @@
       <c r="I56" s="3"/>
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
-    </row>
-    <row r="57" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L56" s="3"/>
+    </row>
+    <row r="57" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>343000</v>
+      </c>
+      <c r="E57" s="3">
         <v>480800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>331200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>356100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>243500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>369600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>402600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>489000</v>
       </c>
-      <c r="K57" s="3"/>
-    </row>
-    <row r="58" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L57" s="3"/>
+    </row>
+    <row r="58" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>398900</v>
+      </c>
+      <c r="E58" s="3">
         <v>318400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>416400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>239900</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>194600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>179100</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>73100</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>50900</v>
       </c>
-      <c r="K58" s="3"/>
-    </row>
-    <row r="59" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L58" s="3"/>
+    </row>
+    <row r="59" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>72800</v>
+      </c>
+      <c r="E59" s="3">
         <v>212500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>131600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>187500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>79200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>47300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>24100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>134500</v>
       </c>
-      <c r="K59" s="3"/>
-    </row>
-    <row r="60" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L59" s="3"/>
+    </row>
+    <row r="60" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>825500</v>
+      </c>
+      <c r="E60" s="3">
         <v>1040000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>915500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>815700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>525200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>597700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>504600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>688600</v>
       </c>
-      <c r="K60" s="3"/>
-    </row>
-    <row r="61" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L60" s="3"/>
+    </row>
+    <row r="61" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1731700</v>
+      </c>
+      <c r="E61" s="3">
         <v>2491600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>740300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1428700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1701500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2200400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>3061000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>3227200</v>
       </c>
-      <c r="K61" s="3"/>
-    </row>
-    <row r="62" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L61" s="3"/>
+    </row>
+    <row r="62" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>417400</v>
+      </c>
+      <c r="E62" s="3">
         <v>455200</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>498500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>731500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>773700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>863400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>917600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1101300</v>
       </c>
-      <c r="K62" s="3"/>
-    </row>
-    <row r="63" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L62" s="3"/>
+    </row>
+    <row r="63" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2065,9 +2213,12 @@
       <c r="J63" s="3">
         <v>0</v>
       </c>
-      <c r="K63" s="3"/>
-    </row>
-    <row r="64" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K63" s="3">
+        <v>0</v>
+      </c>
+      <c r="L63" s="3"/>
+    </row>
+    <row r="64" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2092,9 +2243,12 @@
       <c r="J64" s="3">
         <v>0</v>
       </c>
-      <c r="K64" s="3"/>
-    </row>
-    <row r="65" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K64" s="3">
+        <v>0</v>
+      </c>
+      <c r="L64" s="3"/>
+    </row>
+    <row r="65" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2119,36 +2273,42 @@
       <c r="J65" s="3">
         <v>0</v>
       </c>
-      <c r="K65" s="3"/>
-    </row>
-    <row r="66" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K65" s="3">
+        <v>0</v>
+      </c>
+      <c r="L65" s="3"/>
+    </row>
+    <row r="66" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>3468100</v>
+      </c>
+      <c r="E66" s="3">
         <v>4473800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2211400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2975800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>3000400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>3661500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>4483300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>5456100</v>
       </c>
-      <c r="K66" s="3"/>
-    </row>
-    <row r="67" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L66" s="3"/>
+    </row>
+    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2160,8 +2320,9 @@
       <c r="I67" s="3"/>
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
-    </row>
-    <row r="68" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L67" s="3"/>
+    </row>
+    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2186,9 +2347,12 @@
       <c r="J68" s="3">
         <v>0</v>
       </c>
-      <c r="K68" s="3"/>
-    </row>
-    <row r="69" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K68" s="3">
+        <v>0</v>
+      </c>
+      <c r="L68" s="3"/>
+    </row>
+    <row r="69" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2213,9 +2377,12 @@
       <c r="J69" s="3">
         <v>0</v>
       </c>
-      <c r="K69" s="3"/>
-    </row>
-    <row r="70" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K69" s="3">
+        <v>0</v>
+      </c>
+      <c r="L69" s="3"/>
+    </row>
+    <row r="70" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2240,9 +2407,12 @@
       <c r="J70" s="3">
         <v>0</v>
       </c>
-      <c r="K70" s="3"/>
-    </row>
-    <row r="71" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K70" s="3">
+        <v>0</v>
+      </c>
+      <c r="L70" s="3"/>
+    </row>
+    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2267,36 +2437,42 @@
       <c r="J71" s="3">
         <v>0</v>
       </c>
-      <c r="K71" s="3"/>
-    </row>
-    <row r="72" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K71" s="3">
+        <v>0</v>
+      </c>
+      <c r="L71" s="3"/>
+    </row>
+    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-7098200</v>
+      </c>
+      <c r="E72" s="3">
         <v>-7725500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-7804900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-9362900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-11117600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-8971900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-7744100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-6181300</v>
       </c>
-      <c r="K72" s="3"/>
-    </row>
-    <row r="73" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L72" s="3"/>
+    </row>
+    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2321,9 +2497,12 @@
       <c r="J73" s="3">
         <v>0</v>
       </c>
-      <c r="K73" s="3"/>
-    </row>
-    <row r="74" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K73" s="3">
+        <v>0</v>
+      </c>
+      <c r="L73" s="3"/>
+    </row>
+    <row r="74" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2348,9 +2527,12 @@
       <c r="J74" s="3">
         <v>0</v>
       </c>
-      <c r="K74" s="3"/>
-    </row>
-    <row r="75" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K74" s="3">
+        <v>0</v>
+      </c>
+      <c r="L74" s="3"/>
+    </row>
+    <row r="75" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2375,36 +2557,42 @@
       <c r="J75" s="3">
         <v>0</v>
       </c>
-      <c r="K75" s="3"/>
-    </row>
-    <row r="76" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K75" s="3">
+        <v>0</v>
+      </c>
+      <c r="L75" s="3"/>
+    </row>
+    <row r="76" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>4698900</v>
+      </c>
+      <c r="E76" s="3">
         <v>5200200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>4797800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>4271300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>2215400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>4119200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>4846200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>7306500</v>
       </c>
-      <c r="K76" s="3"/>
-    </row>
-    <row r="77" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L76" s="3"/>
+    </row>
+    <row r="77" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2429,68 +2617,77 @@
       <c r="J77" s="3">
         <v>0</v>
       </c>
-      <c r="K77" s="3"/>
-    </row>
-    <row r="79" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K77" s="3">
+        <v>0</v>
+      </c>
+      <c r="L77" s="3"/>
+    </row>
+    <row r="79" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44561</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44196</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43830</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43465</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43100</v>
       </c>
-      <c r="K80" s="2"/>
-    </row>
-    <row r="81" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L80" s="2"/>
+    </row>
+    <row r="81" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>189900</v>
+      </c>
+      <c r="E81" s="3">
         <v>431800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1096000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1868100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-1977600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-796700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-1917800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-98900</v>
       </c>
-      <c r="K81" s="3"/>
-    </row>
-    <row r="82" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L81" s="3"/>
+    </row>
+    <row r="82" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2502,35 +2699,39 @@
       <c r="I82" s="3"/>
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
-    </row>
-    <row r="83" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L82" s="3"/>
+    </row>
+    <row r="83" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>930100</v>
+      </c>
+      <c r="E83" s="3">
         <v>677500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>596400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>621200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>559300</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>961300</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>1157000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>1226200</v>
       </c>
-      <c r="K83" s="3"/>
-    </row>
-    <row r="84" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L83" s="3"/>
+    </row>
+    <row r="84" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2555,9 +2756,12 @@
       <c r="J84" s="3">
         <v>0</v>
       </c>
-      <c r="K84" s="3"/>
-    </row>
-    <row r="85" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K84" s="3">
+        <v>0</v>
+      </c>
+      <c r="L84" s="3"/>
+    </row>
+    <row r="85" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2582,9 +2786,12 @@
       <c r="J85" s="3">
         <v>0</v>
       </c>
-      <c r="K85" s="3"/>
-    </row>
-    <row r="86" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K85" s="3">
+        <v>0</v>
+      </c>
+      <c r="L85" s="3"/>
+    </row>
+    <row r="86" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2609,9 +2816,12 @@
       <c r="J86" s="3">
         <v>0</v>
       </c>
-      <c r="K86" s="3"/>
-    </row>
-    <row r="87" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K86" s="3">
+        <v>0</v>
+      </c>
+      <c r="L86" s="3"/>
+    </row>
+    <row r="87" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2636,9 +2846,12 @@
       <c r="J87" s="3">
         <v>0</v>
       </c>
-      <c r="K87" s="3"/>
-    </row>
-    <row r="88" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K87" s="3">
+        <v>0</v>
+      </c>
+      <c r="L87" s="3"/>
+    </row>
+    <row r="88" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -2663,36 +2876,42 @@
       <c r="J88" s="3">
         <v>0</v>
       </c>
-      <c r="K88" s="3"/>
-    </row>
-    <row r="89" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K88" s="3">
+        <v>0</v>
+      </c>
+      <c r="L88" s="3"/>
+    </row>
+    <row r="89" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1467700</v>
+      </c>
+      <c r="E89" s="3">
         <v>1662600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1619700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1182000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>675300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1343800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1281000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1370500</v>
       </c>
-      <c r="K89" s="3"/>
-    </row>
-    <row r="90" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L89" s="3"/>
+    </row>
+    <row r="90" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -2704,35 +2923,39 @@
       <c r="I90" s="3"/>
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
-    </row>
-    <row r="91" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L90" s="3"/>
+    </row>
+    <row r="91" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1103500</v>
+      </c>
+      <c r="E91" s="3">
         <v>-924200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-759100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-534300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-548400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1014500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1339700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1721700</v>
       </c>
-      <c r="K91" s="3"/>
-    </row>
-    <row r="92" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L91" s="3"/>
+    </row>
+    <row r="92" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -2757,9 +2980,12 @@
       <c r="J92" s="3">
         <v>0</v>
       </c>
-      <c r="K92" s="3"/>
-    </row>
-    <row r="93" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K92" s="3">
+        <v>0</v>
+      </c>
+      <c r="L92" s="3"/>
+    </row>
+    <row r="93" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -2784,36 +3010,42 @@
       <c r="J93" s="3">
         <v>0</v>
       </c>
-      <c r="K93" s="3"/>
-    </row>
-    <row r="94" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K93" s="3">
+        <v>0</v>
+      </c>
+      <c r="L93" s="3"/>
+    </row>
+    <row r="94" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-364900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-3208500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-635900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-943000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-211100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-266000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1106200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1563100</v>
       </c>
-      <c r="K94" s="3"/>
-    </row>
-    <row r="95" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L94" s="3"/>
+    </row>
+    <row r="95" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -2825,35 +3057,39 @@
       <c r="I95" s="3"/>
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
-    </row>
-    <row r="96" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L95" s="3"/>
+    </row>
+    <row r="96" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>124300</v>
+        <v>197800</v>
       </c>
       <c r="E96" s="3">
+        <v>160500</v>
+      </c>
+      <c r="F96" s="3">
         <v>133900</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>37800</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>7400</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>17000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>145500</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>157600</v>
       </c>
-      <c r="K96" s="3"/>
-    </row>
-    <row r="97" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L96" s="3"/>
+    </row>
+    <row r="97" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -2878,9 +3114,12 @@
       <c r="J97" s="3">
         <v>0</v>
       </c>
-      <c r="K97" s="3"/>
-    </row>
-    <row r="98" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K97" s="3">
+        <v>0</v>
+      </c>
+      <c r="L97" s="3"/>
+    </row>
+    <row r="98" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -2905,9 +3144,12 @@
       <c r="J98" s="3">
         <v>0</v>
       </c>
-      <c r="K98" s="3"/>
-    </row>
-    <row r="99" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K98" s="3">
+        <v>0</v>
+      </c>
+      <c r="L98" s="3"/>
+    </row>
+    <row r="99" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -2932,88 +3174,100 @@
       <c r="J99" s="3">
         <v>0</v>
       </c>
-      <c r="K99" s="3"/>
-    </row>
-    <row r="100" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K99" s="3">
+        <v>0</v>
+      </c>
+      <c r="L99" s="3"/>
+    </row>
+    <row r="100" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-1103500</v>
+      </c>
+      <c r="E100" s="3">
         <v>1339400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-780200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-234800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-501900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-1045200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-211000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>232200</v>
       </c>
-      <c r="K100" s="3"/>
-    </row>
-    <row r="101" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L100" s="3"/>
+    </row>
+    <row r="101" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3" t="s">
+      <c r="D101" s="3">
+        <v>600</v>
+      </c>
+      <c r="E101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>600</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-400</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-500</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>1600</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-600</v>
       </c>
-      <c r="K101" s="3"/>
-    </row>
-    <row r="102" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L101" s="3"/>
+    </row>
+    <row r="102" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E102" s="3">
         <v>-206400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>204200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>3700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-37700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>32100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-34500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>39100</v>
       </c>
-      <c r="K102" s="3"/>
+      <c r="L102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
